--- a/companies/xai-spacex/financials/xai-spacex_model_2026-08-14.xlsx
+++ b/companies/xai-spacex/financials/xai-spacex_model_2026-08-14.xlsx
@@ -1417,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J15"/>
+  <dimension ref="B2:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1581,16 +1581,16 @@
     <row r="10">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Equity raised</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr"/>
       <c r="D10" s="30" t="n">
-        <v>47.16</v>
+        <v>24</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1600,79 +1600,75 @@
       </c>
       <c r="J10" s="29" t="inlineStr">
         <is>
-          <t>pre-merger cumulative</t>
+          <t>PitchBook deal 250364-53T (Early Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Annualised revenue</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr"/>
       <c r="D11" s="30" t="n">
-        <v>3.2</v>
+        <v>50</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J11" s="29" t="inlineStr">
         <is>
-          <t>SEC S-1: AI segment FY2025 revenue (xAI + X)</t>
+          <t>PitchBook deal 275999-77T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Segment detail</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI segment FY25: $3.2B rev, -$6.36B op, capex $12.7B; Q1-26 </t>
-        </is>
+      <c r="D12" s="30" t="n">
+        <v>75</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J12" s="29" t="inlineStr">
         <is>
-          <t>SEC S-1 + Q1 filing</t>
+          <t>PitchBook deal 285233-05T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Listing</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public within SPCX since Jun 12, 2026; broke $135 IPO price </t>
-        </is>
+      <c r="D13" s="30" t="n">
+        <v>230</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1682,25 +1678,23 @@
       </c>
       <c r="J13" s="29" t="inlineStr">
         <is>
-          <t>cross-confirmed press (event T2; level disputed)</t>
+          <t>PitchBook deal 299882-17T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Next print</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>SPCX Q2 2026 earnings Aug 6, 2026: first public frontier-AI-</t>
-        </is>
+      <c r="D14" s="30" t="n">
+        <v>250</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1710,31 +1704,249 @@
       </c>
       <c r="J14" s="29" t="inlineStr">
         <is>
-          <t>canonical refresh, July 16, 2026</t>
+          <t>PitchBook deal 320646-07T (Merger/Acquisition)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Quality score (composite)</t>
+          <t>Equity raised</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr"/>
       <c r="D15" s="30" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J15" s="29" t="inlineStr">
+        <is>
+          <t>pre-merger cumulative</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Last completed round</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Merger/Acquisition $250000M (round n/a)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook deal 320646-07T</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Raised to date ($bn)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="30" t="n">
+        <v>47.163</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook Raised to Date, deal 320646-07T</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Deal history</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr"/>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>2024-01-11 Early Stage VC $135M; 2024-05-26 Early Stage VC $</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J18" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook deal history</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Annualised revenue</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr"/>
+      <c r="D19" s="30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="J19" s="29" t="inlineStr">
+        <is>
+          <t>SEC S-1: AI segment FY2025 revenue (xAI + X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Segment detail</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr"/>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI segment FY25: $3.2B rev, -$6.36B op, capex $12.7B; Q1-26 </t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="J20" s="29" t="inlineStr">
+        <is>
+          <t>SEC S-1 + Q1 filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public within SPCX since Jun 12, 2026; broke $135 IPO price </t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J21" s="29" t="inlineStr">
+        <is>
+          <t>cross-confirmed press (event T2; level disputed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Next print</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr"/>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>SPCX Q2 2026 earnings Aug 6, 2026: first public frontier-AI-</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J22" s="29" t="inlineStr">
+        <is>
+          <t>canonical refresh, July 16, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Quality score (composite)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr"/>
+      <c r="D23" s="30" t="n">
         <v>4.49</v>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr">
+      <c r="J23" s="29" t="inlineStr">
         <is>
           <t>internal AIBQ v3.0 (this desk)</t>
         </is>
